--- a/data/trans_dic/P19F$tarde-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P19F$tarde-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se cepilla los dientes por la tarde</t>
+          <t>Población que, al menos, se cepilla los dientes por la tarde (tasa de respuesta: 93,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24,86; 34,05</t>
+          <t>25,02; 34,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23,88; 31,54</t>
+          <t>22,99; 31,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,13; 31,45</t>
+          <t>25,26; 31,08</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,76; 34,29</t>
+          <t>28,76; 34,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,36; 36,33</t>
+          <t>29,96; 36,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,21; 34,21</t>
+          <t>30,29; 34,33</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24,47; 36,52</t>
+          <t>25,11; 37,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31,53; 45,69</t>
+          <t>31,42; 45,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,68; 39,5</t>
+          <t>29,53; 38,85</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,55; 32,89</t>
+          <t>28,57; 33,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,88; 34,48</t>
+          <t>29,5; 34,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29,85; 32,93</t>
+          <t>29,87; 33,04</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se cepilla los dientes por la tarde</t>
+          <t>Población que, al menos, se cepilla los dientes por la tarde (tasa de respuesta: 93,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>97498; 133539</t>
+          <t>98115; 134131</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>127313; 168121</t>
+          <t>122538; 167476</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>232546; 290959</t>
+          <t>233732; 287518</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>325897; 388644</t>
+          <t>325962; 386623</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>304762; 364626</t>
+          <t>300751; 362070</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>645586; 730986</t>
+          <t>647330; 733712</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>59427; 88676</t>
+          <t>60967; 91819</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>64273; 93132</t>
+          <t>64032; 92479</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>132583; 176405</t>
+          <t>131903; 173522</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>504862; 581529</t>
+          <t>505117; 588413</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>520103; 600080</t>
+          <t>513473; 598215</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1047351; 1155484</t>
+          <t>1048159; 1159363</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19F$tarde-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P19F$tarde-Estudios-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25,02; 34,21</t>
+          <t>24,46; 34,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,99; 31,42</t>
+          <t>24,0; 31,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,26; 31,08</t>
+          <t>25,15; 31,19</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,76; 34,12</t>
+          <t>28,74; 34,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29,96; 36,07</t>
+          <t>30,5; 36,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,29; 34,33</t>
+          <t>30,34; 34,41</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25,11; 37,81</t>
+          <t>24,89; 37,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31,42; 45,37</t>
+          <t>31,77; 45,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,53; 38,85</t>
+          <t>30,07; 38,88</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,57; 33,28</t>
+          <t>28,51; 33,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,5; 34,37</t>
+          <t>29,89; 34,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29,87; 33,04</t>
+          <t>29,88; 32,99</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>98115; 134131</t>
+          <t>95933; 133708</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>122538; 167476</t>
+          <t>127923; 168243</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>233732; 287518</t>
+          <t>232676; 288596</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>325962; 386623</t>
+          <t>325690; 387819</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>300751; 362070</t>
+          <t>306138; 363925</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>647330; 733712</t>
+          <t>648247; 735331</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>60967; 91819</t>
+          <t>60451; 90366</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>64032; 92479</t>
+          <t>64748; 92462</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>131903; 173522</t>
+          <t>134313; 173661</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>505117; 588413</t>
+          <t>504189; 586174</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>513473; 598215</t>
+          <t>520207; 597990</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1048159; 1159363</t>
+          <t>1048482; 1157539</t>
         </is>
       </c>
     </row>
